--- a/healthcare_forms/042_nursing_practices_audit_form--healthcare_forms.xlsx
+++ b/healthcare_forms/042_nursing_practices_audit_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Page 1</t>
+          <t>Nursing Practices Audit Form</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_1</t>
+          <t>page_two</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nursing Practices Audit</t>
+          <t>Which of the following nursing practices have been evaluated?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>patient_care_plan</t>
+          <t>page_three</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Patient Care Plan</t>
+          <t>Has the patient's care plan been reviewed?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>evaluation_date</t>
+          <t>page_four</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Evaluation Date</t>
+          <t>Page Four</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>evaluation_time</t>
+          <t>page_five</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Evaluation Time</t>
+          <t>Has the patient's care plan been completed?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_2</t>
+          <t>page_six</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nursing Practices Audit</t>
+          <t>Page Six</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,19 +658,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_3</t>
+          <t>page_seven</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Please select one or more items</t>
-        </is>
-      </c>
+          <t>Page Seven</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -680,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>page_eight</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Page Eight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>page_nine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Page Nine</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>page_ten</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Page Ten</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phone_2</t>
+          <t>page_eleven</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phone 2</t>
+          <t>Page Eleven</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -777,553 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_4</t>
+          <t>page_twelve</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nursing Practices Audit</t>
+          <t>Page Twelve</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_5</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_6</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_7</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_8</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_9</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_10</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_11</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_12</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_13</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_14</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_15</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_16</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_17</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Please select one or more items</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_18</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_19</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_20</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_21</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_22</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_23</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_24</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_25</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Nursing Practices Audit</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Please select one or more items</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>page_two</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Page 2</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>page_three</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Page 3</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1340,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1368,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_1_choices</t>
+          <t>page_two_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1385,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_1_choices</t>
+          <t>page_two_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1402,143 +861,143 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_2_choices</t>
+          <t>page_two_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_2_choices</t>
+          <t>page_three_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_2_choices</t>
+          <t>page_three_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_2_choices</t>
+          <t>page_four_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_3_choices</t>
+          <t>page_four_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_3_choices</t>
+          <t>page_four_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_3_choices</t>
+          <t>page_five_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_3_choices</t>
+          <t>page_five_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_4_choices</t>
+          <t>page_six_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1555,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_4_choices</t>
+          <t>page_six_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1572,75 +1031,75 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_5_choices</t>
+          <t>page_six_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_5_choices</t>
+          <t>page_seven_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_6_choices</t>
+          <t>page_seven_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_6_choices</t>
+          <t>page_seven_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_7_choices</t>
+          <t>page_eight_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1657,7 +1116,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_7_choices</t>
+          <t>page_eight_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1674,7 +1133,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_8_choices</t>
+          <t>page_nine_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,7 +1150,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_8_choices</t>
+          <t>page_nine_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1708,75 +1167,75 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_9_choices</t>
+          <t>page_nine_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_9_choices</t>
+          <t>page_ten_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_10_choices</t>
+          <t>page_ten_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_10_choices</t>
+          <t>page_ten_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_11_choices</t>
+          <t>page_eleven_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1793,7 +1252,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_11_choices</t>
+          <t>page_eleven_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1810,476 +1269,68 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_12_choices</t>
+          <t>page_eleven_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_12_choices</t>
+          <t>page_twelve_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_13_choices</t>
+          <t>page_twelve_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nursing_practices_audit_form_fields_13_choices</t>
+          <t>page_twelve_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_14_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_14_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_15_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_15_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_16_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_16_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_17_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_17_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_18_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_18_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_19_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_19_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_20_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_20_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_21_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_21_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_22_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_22_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_23_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_23_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_24_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_24_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_25_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>nursing_practices_audit_form_fields_25_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
